--- a/data/trans_orig/Q5410-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>284853</t>
+          <t>285652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>291773</t>
+          <t>291770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>333360</t>
+          <t>332111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>341898</t>
+          <t>341884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>622426</t>
+          <t>621949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>632769</t>
+          <t>632720</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>198314</t>
+          <t>198085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207979</t>
+          <t>208031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>302142</t>
+          <t>302106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>321349</t>
+          <t>321547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>506451</t>
+          <t>505701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>527429</t>
+          <t>526569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488130</t>
+          <t>487510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498253</t>
+          <t>498172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640852</t>
+          <t>639905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>661170</t>
+          <t>661311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1133421</t>
+          <t>1133097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1157292</t>
+          <t>1156210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>298963</t>
+          <t>298734</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>307818</t>
+          <t>307865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>337290</t>
+          <t>338167</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>349924</t>
+          <t>349988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>641825</t>
+          <t>640728</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>656751</t>
+          <t>655807</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>11654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>27975</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32967</t>
+          <t>33733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>27645</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43403</t>
+          <t>43687</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>218062</t>
+          <t>217670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>237127</t>
+          <t>238072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>343614</t>
+          <t>343835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>366973</t>
+          <t>367279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>568702</t>
+          <t>568849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>599077</t>
+          <t>600638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>31211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39621</t>
+          <t>41375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31013</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>52133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>524191</t>
+          <t>522665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>544707</t>
+          <t>543920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>686967</t>
+          <t>689004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>713631</t>
+          <t>714049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1217257</t>
+          <t>1219230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1251653</t>
+          <t>1252825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>324933</t>
+          <t>324565</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>333364</t>
+          <t>333314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>366785</t>
+          <t>366121</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>375757</t>
+          <t>375767</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>694849</t>
+          <t>694840</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>707854</t>
+          <t>707250</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>235667</t>
+          <t>234412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>248897</t>
+          <t>248707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>370252</t>
+          <t>370248</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>389549</t>
+          <t>389542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>610810</t>
+          <t>611633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>635087</t>
+          <t>634618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38215</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>565250</t>
+          <t>563887</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>580081</t>
+          <t>580085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742830</t>
+          <t>741490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763494</t>
+          <t>763083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1313810</t>
+          <t>1314356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1340273</t>
+          <t>1340697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>921</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>361958</t>
+          <t>400503</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>356657</t>
+          <t>395265</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>365315</t>
+          <t>403835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>603427</t>
+          <t>433852</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>598843</t>
+          <t>429295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>606993</t>
+          <t>436127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>965386</t>
+          <t>834354</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>959440</t>
+          <t>827115</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>972051</t>
+          <t>838696</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -6091,102 +6091,102 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>31646</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>23371</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>40040</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>38675</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>30740</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>49414</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>3,98%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>28480</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>21843</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36300</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>34966</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>27693</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>44663</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>273133</t>
+          <t>299859</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>268130</t>
+          <t>294657</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>276833</t>
+          <t>303969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>386769</t>
+          <t>420991</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>377706</t>
+          <t>410597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>394183</t>
+          <t>430581</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>659901</t>
+          <t>720850</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>648906</t>
+          <t>708776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>668974</t>
+          <t>730700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425334</t>
+          <t>464005</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425334</t>
+          <t>464005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425334</t>
+          <t>464005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>706742</t>
+          <t>772664</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>706742</t>
+          <t>772664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706742</t>
+          <t>772664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>44205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>47485</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28321</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>59237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>635090</t>
+          <t>700361</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>627740</t>
+          <t>693034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639778</t>
+          <t>705665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>990196</t>
+          <t>854843</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>975036</t>
+          <t>843069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1011681</t>
+          <t>864204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1625287</t>
+          <t>1555204</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1611057</t>
+          <t>1542681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1645514</t>
+          <t>1565827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
